--- a/서버정보/20261001_리소스배포_개발.xlsx
+++ b/서버정보/20261001_리소스배포_개발.xlsx
@@ -17282,12 +17282,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -17431,6 +17425,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
@@ -17440,22 +17440,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -17471,4 +17455,20 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/서버정보/20261001_리소스배포_개발.xlsx
+++ b/서버정보/20261001_리소스배포_개발.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8AB8530-5B42-4B91-B32C-206256D3CA5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25D5746A-953F-4EBF-905A-C4671FB58583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -573,7 +573,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2548" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2480" uniqueCount="448">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1975,29 +1975,6 @@
   </si>
   <si>
     <t>az-d-int-host4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.156.147.4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.156.147.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.156.147.6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.156.147.7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>d-puls-ap-sbn</t>
-  </si>
-  <si>
-    <t>/subscriptions/38befed7-7226-4784-910e-0cea5422077d/resourceGroups/hazr-d-dch-rg/providers/Microsoft.Compute/galleries/temp_ertest_gallery/images/temp_ertest_vm_image/versions/0.0.2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3145,8 +3122,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="B1:AF69" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
-  <autoFilter ref="B1:AF69" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="B1:AF65" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
+  <autoFilter ref="B1:AF65" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="31">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Stage" dataDxfId="31"/>
     <tableColumn id="2" xr3:uid="{DD2076C4-D866-4329-BEA8-1D816DAF3627}" name="Role" dataDxfId="30">
@@ -4276,7 +4253,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF69"/>
+  <dimension ref="A1:AF65"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" style="18" customWidth="1"/>
@@ -9038,31 +9015,32 @@
     <row r="54" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A54" s="21"/>
       <c r="B54" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>391</v>
+        <v>396</v>
+      </c>
+      <c r="C54" s="1" t="str" cm="1">
+        <f t="array" ref="C54">UPPER(INDEX(_xlfn.TEXTSPLIT($D54, "-"), 3))</f>
+        <v>IF</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>301</v>
+        <v>55</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>184</v>
+        <v>387</v>
       </c>
       <c r="I54" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J54" s="1">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="K54" s="1" t="s">
         <v>302</v>
@@ -9071,14 +9049,14 @@
         <v>182</v>
       </c>
       <c r="M54" s="9" t="s">
-        <v>374</v>
+        <v>399</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="O54" s="1" t="str">
-        <f t="shared" ref="O54:O59" si="8">SUBSTITUTE(F54,"hazr-","")&amp;"-osdisk"</f>
-        <v>az-d-int-host1-osdisk</v>
+        <f t="shared" ref="O54:O55" si="8">SUBSTITUTE(F54,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-if-edmsstr01-osdisk</v>
       </c>
       <c r="P54" s="1">
         <v>64</v>
@@ -9090,8 +9068,8 @@
       <c r="S54" s="1"/>
       <c r="T54" s="1"/>
       <c r="U54" s="1" t="str">
-        <f t="shared" ref="U54:U59" si="9">SUBSTITUTE(F54,"hazr-","")&amp;"-nic"</f>
-        <v>az-d-int-host1-nic</v>
+        <f t="shared" ref="U54:U55" si="9">SUBSTITUTE(F54,"hazr-","")&amp;"-nic"</f>
+        <v>d-if-edmsstr01-nic</v>
       </c>
       <c r="V54" s="1" t="b">
         <v>1</v>
@@ -9103,10 +9081,10 @@
         <v>49</v>
       </c>
       <c r="Y54" s="1" t="s">
-        <v>57</v>
+        <v>401</v>
       </c>
       <c r="Z54" s="1" t="s">
-        <v>98</v>
+        <v>402</v>
       </c>
       <c r="AA54" s="1" t="b">
         <v>1</v>
@@ -9126,22 +9104,23 @@
     <row r="55" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A55" s="21"/>
       <c r="B55" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>391</v>
+        <v>407</v>
+      </c>
+      <c r="C55" s="1" t="str" cm="1">
+        <f t="array" ref="C55">UPPER(INDEX(_xlfn.TEXTSPLIT($D55, "-"), 3))</f>
+        <v>SEC</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>301</v>
+        <v>408</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>393</v>
+        <v>409</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>397</v>
+        <v>410</v>
       </c>
       <c r="H55" s="10" t="s">
         <v>184</v>
@@ -9159,14 +9138,14 @@
         <v>182</v>
       </c>
       <c r="M55" s="9" t="s">
-        <v>374</v>
+        <v>411</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>401</v>
+        <v>416</v>
       </c>
       <c r="O55" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>az-d-int-host2-osdisk</v>
+        <v>d-sec-mevrsol01-osdisk</v>
       </c>
       <c r="P55" s="1">
         <v>64</v>
@@ -9179,7 +9158,7 @@
       <c r="T55" s="1"/>
       <c r="U55" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>az-d-int-host2-nic</v>
+        <v>d-sec-mevrsol01-nic</v>
       </c>
       <c r="V55" s="1" t="b">
         <v>1</v>
@@ -9188,13 +9167,13 @@
         <v>1</v>
       </c>
       <c r="X55" s="1" t="s">
-        <v>49</v>
+        <v>412</v>
       </c>
       <c r="Y55" s="1" t="s">
         <v>57</v>
       </c>
       <c r="Z55" s="1" t="s">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="AA55" s="1" t="b">
         <v>1</v>
@@ -9212,27 +9191,27 @@
       <c r="AF55" s="1"/>
     </row>
     <row r="56" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A56" s="21"/>
       <c r="B56" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>391</v>
+        <v>417</v>
+      </c>
+      <c r="C56" s="1" t="str" cm="1">
+        <f t="array" ref="C56">UPPER(INDEX(_xlfn.TEXTSPLIT($D56, "-"), 3))</f>
+        <v>CLV</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>301</v>
+        <v>428</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>394</v>
+        <v>434</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>398</v>
+        <v>429</v>
       </c>
       <c r="H56" s="10" t="s">
-        <v>184</v>
+        <v>419</v>
       </c>
       <c r="I56" s="1">
         <v>2</v>
@@ -9247,14 +9226,14 @@
         <v>182</v>
       </c>
       <c r="M56" s="9" t="s">
-        <v>374</v>
+        <v>420</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>401</v>
+        <v>439</v>
       </c>
       <c r="O56" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>az-d-int-host3-osdisk</v>
+        <f>SUBSTITUTE(F56,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-clv-web01-osdisk</v>
       </c>
       <c r="P56" s="1">
         <v>64</v>
@@ -9266,8 +9245,8 @@
       <c r="S56" s="1"/>
       <c r="T56" s="1"/>
       <c r="U56" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>az-d-int-host3-nic</v>
+        <f>SUBSTITUTE(F56,"hazr-","")&amp;"-nic"</f>
+        <v>d-clv-web01-nic</v>
       </c>
       <c r="V56" s="1" t="b">
         <v>1</v>
@@ -9279,10 +9258,10 @@
         <v>49</v>
       </c>
       <c r="Y56" s="1" t="s">
-        <v>57</v>
+        <v>421</v>
       </c>
       <c r="Z56" s="1" t="s">
-        <v>400</v>
+        <v>440</v>
       </c>
       <c r="AA56" s="1" t="b">
         <v>1</v>
@@ -9300,27 +9279,27 @@
       <c r="AF56" s="1"/>
     </row>
     <row r="57" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A57" s="21"/>
       <c r="B57" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>391</v>
+        <v>417</v>
+      </c>
+      <c r="C57" s="1" t="str" cm="1">
+        <f t="array" ref="C57">UPPER(INDEX(_xlfn.TEXTSPLIT($D57, "-"), 3))</f>
+        <v>CLV</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>301</v>
+        <v>428</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>395</v>
+        <v>435</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>399</v>
+        <v>430</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>184</v>
+        <v>419</v>
       </c>
       <c r="I57" s="1">
         <v>2</v>
@@ -9335,14 +9314,14 @@
         <v>182</v>
       </c>
       <c r="M57" s="9" t="s">
-        <v>374</v>
+        <v>420</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>401</v>
+        <v>439</v>
       </c>
       <c r="O57" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>az-d-int-host4-osdisk</v>
+        <f>SUBSTITUTE(F57,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-clv-ap01-osdisk</v>
       </c>
       <c r="P57" s="1">
         <v>64</v>
@@ -9354,8 +9333,8 @@
       <c r="S57" s="1"/>
       <c r="T57" s="1"/>
       <c r="U57" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>az-d-int-host4-nic</v>
+        <f>SUBSTITUTE(F57,"hazr-","")&amp;"-nic"</f>
+        <v>d-clv-ap01-nic</v>
       </c>
       <c r="V57" s="1" t="b">
         <v>1</v>
@@ -9370,7 +9349,7 @@
         <v>57</v>
       </c>
       <c r="Z57" s="1" t="s">
-        <v>98</v>
+        <v>441</v>
       </c>
       <c r="AA57" s="1" t="b">
         <v>1</v>
@@ -9388,34 +9367,33 @@
       <c r="AF57" s="1"/>
     </row>
     <row r="58" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A58" s="21"/>
       <c r="B58" s="1" t="s">
-        <v>402</v>
+        <v>417</v>
       </c>
       <c r="C58" s="1" t="str" cm="1">
         <f t="array" ref="C58">UPPER(INDEX(_xlfn.TEXTSPLIT($D58, "-"), 3))</f>
-        <v>IF</v>
+        <v>CLV</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>55</v>
+        <v>428</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>403</v>
+        <v>436</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>404</v>
+        <v>431</v>
       </c>
       <c r="H58" s="10" t="s">
-        <v>387</v>
+        <v>195</v>
       </c>
       <c r="I58" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J58" s="1">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="K58" s="1" t="s">
         <v>302</v>
@@ -9424,14 +9402,14 @@
         <v>182</v>
       </c>
       <c r="M58" s="9" t="s">
-        <v>405</v>
+        <v>420</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>406</v>
+        <v>439</v>
       </c>
       <c r="O58" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>d-if-edmsstr01-osdisk</v>
+        <f>SUBSTITUTE(F58,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-clv-ssrap01-osdisk</v>
       </c>
       <c r="P58" s="1">
         <v>64</v>
@@ -9443,8 +9421,8 @@
       <c r="S58" s="1"/>
       <c r="T58" s="1"/>
       <c r="U58" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>d-if-edmsstr01-nic</v>
+        <f>SUBSTITUTE(F58,"hazr-","")&amp;"-nic"</f>
+        <v>d-clv-ssrap01-nic</v>
       </c>
       <c r="V58" s="1" t="b">
         <v>1</v>
@@ -9456,10 +9434,10 @@
         <v>49</v>
       </c>
       <c r="Y58" s="1" t="s">
-        <v>407</v>
+        <v>57</v>
       </c>
       <c r="Z58" s="1" t="s">
-        <v>408</v>
+        <v>441</v>
       </c>
       <c r="AA58" s="1" t="b">
         <v>1</v>
@@ -9477,28 +9455,27 @@
       <c r="AF58" s="1"/>
     </row>
     <row r="59" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A59" s="21"/>
       <c r="B59" s="1" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="C59" s="1" t="str" cm="1">
         <f t="array" ref="C59">UPPER(INDEX(_xlfn.TEXTSPLIT($D59, "-"), 3))</f>
-        <v>SEC</v>
+        <v>CLV</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>415</v>
+        <v>437</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>416</v>
+        <v>432</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="I59" s="1">
         <v>2</v>
@@ -9513,14 +9490,14 @@
         <v>182</v>
       </c>
       <c r="M59" s="9" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>422</v>
+        <v>439</v>
       </c>
       <c r="O59" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>d-sec-mevrsol01-osdisk</v>
+        <f>SUBSTITUTE(F59,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-clv-admweb01-osdisk</v>
       </c>
       <c r="P59" s="1">
         <v>64</v>
@@ -9532,8 +9509,8 @@
       <c r="S59" s="1"/>
       <c r="T59" s="1"/>
       <c r="U59" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>d-sec-mevrsol01-nic</v>
+        <f>SUBSTITUTE(F59,"hazr-","")&amp;"-nic"</f>
+        <v>d-clv-admweb01-nic</v>
       </c>
       <c r="V59" s="1" t="b">
         <v>1</v>
@@ -9542,13 +9519,13 @@
         <v>1</v>
       </c>
       <c r="X59" s="1" t="s">
-        <v>418</v>
+        <v>49</v>
       </c>
       <c r="Y59" s="1" t="s">
         <v>57</v>
       </c>
       <c r="Z59" s="1" t="s">
-        <v>419</v>
+        <v>441</v>
       </c>
       <c r="AA59" s="1" t="b">
         <v>1</v>
@@ -9567,26 +9544,26 @@
     </row>
     <row r="60" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B60" s="1" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="C60" s="1" t="str" cm="1">
         <f t="array" ref="C60">UPPER(INDEX(_xlfn.TEXTSPLIT($D60, "-"), 3))</f>
         <v>CLV</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H60" s="10" t="s">
-        <v>425</v>
+        <v>195</v>
       </c>
       <c r="I60" s="1">
         <v>2</v>
@@ -9601,14 +9578,14 @@
         <v>182</v>
       </c>
       <c r="M60" s="9" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="O60" s="1" t="str">
         <f>SUBSTITUTE(F60,"hazr-","")&amp;"-osdisk"</f>
-        <v>d-clv-web01-osdisk</v>
+        <v>d-clv-admap01-osdisk</v>
       </c>
       <c r="P60" s="1">
         <v>64</v>
@@ -9621,7 +9598,7 @@
       <c r="T60" s="1"/>
       <c r="U60" s="1" t="str">
         <f>SUBSTITUTE(F60,"hazr-","")&amp;"-nic"</f>
-        <v>d-clv-web01-nic</v>
+        <v>d-clv-admap01-nic</v>
       </c>
       <c r="V60" s="1" t="b">
         <v>1</v>
@@ -9633,10 +9610,10 @@
         <v>49</v>
       </c>
       <c r="Y60" s="1" t="s">
-        <v>427</v>
+        <v>57</v>
       </c>
       <c r="Z60" s="1" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="AA60" s="1" t="b">
         <v>1</v>
@@ -9655,26 +9632,26 @@
     </row>
     <row r="61" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B61" s="1" t="s">
-        <v>423</v>
+        <v>31</v>
       </c>
       <c r="C61" s="1" t="str" cm="1">
         <f t="array" ref="C61">UPPER(INDEX(_xlfn.TEXTSPLIT($D61, "-"), 3))</f>
-        <v>CLV</v>
+        <v>IF</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>434</v>
+        <v>55</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F61" s="1" t="s">
-        <v>441</v>
+      <c r="F61" s="38" t="s">
+        <v>446</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>425</v>
+        <v>388</v>
       </c>
       <c r="I61" s="1">
         <v>2</v>
@@ -9686,17 +9663,17 @@
         <v>302</v>
       </c>
       <c r="L61" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M61" s="9" t="s">
-        <v>426</v>
+        <v>374</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="O61" s="1" t="str">
-        <f>SUBSTITUTE(F61,"hazr-","")&amp;"-osdisk"</f>
-        <v>d-clv-ap01-osdisk</v>
+        <f t="shared" ref="O61:O65" si="10">SUBSTITUTE(F61,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-if-brpasol01-osdisk</v>
       </c>
       <c r="P61" s="1">
         <v>64</v>
@@ -9708,8 +9685,8 @@
       <c r="S61" s="1"/>
       <c r="T61" s="1"/>
       <c r="U61" s="1" t="str">
-        <f>SUBSTITUTE(F61,"hazr-","")&amp;"-nic"</f>
-        <v>d-clv-ap01-nic</v>
+        <f t="shared" ref="U61:U65" si="11">SUBSTITUTE(F61,"hazr-","")&amp;"-nic"</f>
+        <v>d-if-brpasol01-nic</v>
       </c>
       <c r="V61" s="1" t="b">
         <v>1</v>
@@ -9724,7 +9701,7 @@
         <v>57</v>
       </c>
       <c r="Z61" s="1" t="s">
-        <v>447</v>
+        <v>166</v>
       </c>
       <c r="AA61" s="1" t="b">
         <v>1</v>
@@ -9743,26 +9720,20 @@
     </row>
     <row r="62" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B62" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="C62" s="1" t="str" cm="1">
+        <v>31</v>
+      </c>
+      <c r="C62" s="1" t="e" cm="1">
         <f t="array" ref="C62">UPPER(INDEX(_xlfn.TEXTSPLIT($D62, "-"), 3))</f>
-        <v>CLV</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>434</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D62" s="1"/>
       <c r="E62" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F62" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>437</v>
-      </c>
+      <c r="F62" s="39"/>
+      <c r="G62" s="1"/>
       <c r="H62" s="10" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="I62" s="1">
         <v>2</v>
@@ -9774,17 +9745,15 @@
         <v>302</v>
       </c>
       <c r="L62" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M62" s="9" t="s">
-        <v>426</v>
-      </c>
-      <c r="N62" s="1" t="s">
-        <v>445</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="N62" s="1"/>
       <c r="O62" s="1" t="str">
-        <f>SUBSTITUTE(F62,"hazr-","")&amp;"-osdisk"</f>
-        <v>d-clv-ssrap01-osdisk</v>
+        <f t="shared" si="10"/>
+        <v>-osdisk</v>
       </c>
       <c r="P62" s="1">
         <v>64</v>
@@ -9796,8 +9765,8 @@
       <c r="S62" s="1"/>
       <c r="T62" s="1"/>
       <c r="U62" s="1" t="str">
-        <f>SUBSTITUTE(F62,"hazr-","")&amp;"-nic"</f>
-        <v>d-clv-ssrap01-nic</v>
+        <f t="shared" si="11"/>
+        <v>-nic</v>
       </c>
       <c r="V62" s="1" t="b">
         <v>1</v>
@@ -9809,11 +9778,9 @@
         <v>49</v>
       </c>
       <c r="Y62" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z62" s="1" t="s">
-        <v>447</v>
-      </c>
+        <v>427</v>
+      </c>
+      <c r="Z62" s="1"/>
       <c r="AA62" s="1" t="b">
         <v>1</v>
       </c>
@@ -9831,26 +9798,20 @@
     </row>
     <row r="63" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B63" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="C63" s="1" t="str" cm="1">
+        <v>31</v>
+      </c>
+      <c r="C63" s="1" t="e" cm="1">
         <f t="array" ref="C63">UPPER(INDEX(_xlfn.TEXTSPLIT($D63, "-"), 3))</f>
-        <v>CLV</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>434</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D63" s="1"/>
       <c r="E63" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F63" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>438</v>
-      </c>
+      <c r="F63" s="38"/>
+      <c r="G63" s="1"/>
       <c r="H63" s="10" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="I63" s="1">
         <v>2</v>
@@ -9862,17 +9823,15 @@
         <v>302</v>
       </c>
       <c r="L63" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M63" s="9" t="s">
-        <v>426</v>
-      </c>
-      <c r="N63" s="1" t="s">
-        <v>445</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="N63" s="1"/>
       <c r="O63" s="1" t="str">
-        <f>SUBSTITUTE(F63,"hazr-","")&amp;"-osdisk"</f>
-        <v>d-clv-admweb01-osdisk</v>
+        <f t="shared" si="10"/>
+        <v>-osdisk</v>
       </c>
       <c r="P63" s="1">
         <v>64</v>
@@ -9884,8 +9843,8 @@
       <c r="S63" s="1"/>
       <c r="T63" s="1"/>
       <c r="U63" s="1" t="str">
-        <f>SUBSTITUTE(F63,"hazr-","")&amp;"-nic"</f>
-        <v>d-clv-admweb01-nic</v>
+        <f t="shared" si="11"/>
+        <v>-nic</v>
       </c>
       <c r="V63" s="1" t="b">
         <v>1</v>
@@ -9897,11 +9856,9 @@
         <v>49</v>
       </c>
       <c r="Y63" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z63" s="1" t="s">
-        <v>447</v>
-      </c>
+        <v>427</v>
+      </c>
+      <c r="Z63" s="1"/>
       <c r="AA63" s="1" t="b">
         <v>1</v>
       </c>
@@ -9919,26 +9876,20 @@
     </row>
     <row r="64" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B64" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="C64" s="1" t="str" cm="1">
+        <v>31</v>
+      </c>
+      <c r="C64" s="1" t="e" cm="1">
         <f t="array" ref="C64">UPPER(INDEX(_xlfn.TEXTSPLIT($D64, "-"), 3))</f>
-        <v>CLV</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>434</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D64" s="1"/>
       <c r="E64" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F64" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>439</v>
-      </c>
+      <c r="F64" s="39"/>
+      <c r="G64" s="1"/>
       <c r="H64" s="10" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="I64" s="1">
         <v>2</v>
@@ -9950,17 +9901,15 @@
         <v>302</v>
       </c>
       <c r="L64" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M64" s="9" t="s">
-        <v>426</v>
-      </c>
-      <c r="N64" s="1" t="s">
-        <v>445</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="N64" s="1"/>
       <c r="O64" s="1" t="str">
-        <f>SUBSTITUTE(F64,"hazr-","")&amp;"-osdisk"</f>
-        <v>d-clv-admap01-osdisk</v>
+        <f t="shared" si="10"/>
+        <v>-osdisk</v>
       </c>
       <c r="P64" s="1">
         <v>64</v>
@@ -9972,8 +9921,8 @@
       <c r="S64" s="1"/>
       <c r="T64" s="1"/>
       <c r="U64" s="1" t="str">
-        <f>SUBSTITUTE(F64,"hazr-","")&amp;"-nic"</f>
-        <v>d-clv-admap01-nic</v>
+        <f t="shared" si="11"/>
+        <v>-nic</v>
       </c>
       <c r="V64" s="1" t="b">
         <v>1</v>
@@ -9985,11 +9934,9 @@
         <v>49</v>
       </c>
       <c r="Y64" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z64" s="1" t="s">
-        <v>447</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="Z64" s="1"/>
       <c r="AA64" s="1" t="b">
         <v>1</v>
       </c>
@@ -10009,24 +9956,18 @@
       <c r="B65" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C65" s="1" t="str" cm="1">
+      <c r="C65" s="1" t="e" cm="1">
         <f t="array" ref="C65">UPPER(INDEX(_xlfn.TEXTSPLIT($D65, "-"), 3))</f>
-        <v>IF</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>55</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D65" s="1"/>
       <c r="E65" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F65" s="38" t="s">
-        <v>452</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>453</v>
-      </c>
+      <c r="F65" s="40"/>
+      <c r="G65" s="1"/>
       <c r="H65" s="10" t="s">
-        <v>388</v>
+        <v>184</v>
       </c>
       <c r="I65" s="1">
         <v>2</v>
@@ -10043,12 +9984,10 @@
       <c r="M65" s="9" t="s">
         <v>374</v>
       </c>
-      <c r="N65" s="1" t="s">
-        <v>445</v>
-      </c>
+      <c r="N65" s="1"/>
       <c r="O65" s="1" t="str">
-        <f t="shared" ref="O65:O69" si="10">SUBSTITUTE(F65,"hazr-","")&amp;"-osdisk"</f>
-        <v>d-if-brpasol01-osdisk</v>
+        <f t="shared" si="10"/>
+        <v>-osdisk</v>
       </c>
       <c r="P65" s="1">
         <v>64</v>
@@ -10060,8 +9999,8 @@
       <c r="S65" s="1"/>
       <c r="T65" s="1"/>
       <c r="U65" s="1" t="str">
-        <f t="shared" ref="U65:U69" si="11">SUBSTITUTE(F65,"hazr-","")&amp;"-nic"</f>
-        <v>d-if-brpasol01-nic</v>
+        <f t="shared" si="11"/>
+        <v>-nic</v>
       </c>
       <c r="V65" s="1" t="b">
         <v>1</v>
@@ -10073,11 +10012,9 @@
         <v>49</v>
       </c>
       <c r="Y65" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z65" s="1" t="s">
-        <v>166</v>
-      </c>
+        <v>427</v>
+      </c>
+      <c r="Z65" s="1"/>
       <c r="AA65" s="1" t="b">
         <v>1</v>
       </c>
@@ -10092,318 +10029,6 @@
       </c>
       <c r="AE65" s="1"/>
       <c r="AF65" s="1"/>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B66" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="1" t="e" cm="1">
-        <f t="array" ref="C66">UPPER(INDEX(_xlfn.TEXTSPLIT($D66, "-"), 3))</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D66" s="1"/>
-      <c r="E66" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F66" s="39"/>
-      <c r="G66" s="1"/>
-      <c r="H66" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="I66" s="1">
-        <v>2</v>
-      </c>
-      <c r="J66" s="1">
-        <v>8</v>
-      </c>
-      <c r="K66" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="L66" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="M66" s="9" t="s">
-        <v>374</v>
-      </c>
-      <c r="N66" s="1"/>
-      <c r="O66" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>-osdisk</v>
-      </c>
-      <c r="P66" s="1">
-        <v>64</v>
-      </c>
-      <c r="Q66" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="R66" s="1"/>
-      <c r="S66" s="1"/>
-      <c r="T66" s="1"/>
-      <c r="U66" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v>-nic</v>
-      </c>
-      <c r="V66" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="W66" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="X66" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y66" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="Z66" s="1"/>
-      <c r="AA66" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB66" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AC66" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="AD66" s="1">
-        <v>1</v>
-      </c>
-      <c r="AE66" s="1"/>
-      <c r="AF66" s="1"/>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B67" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="1" t="e" cm="1">
-        <f t="array" ref="C67">UPPER(INDEX(_xlfn.TEXTSPLIT($D67, "-"), 3))</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D67" s="1"/>
-      <c r="E67" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F67" s="38"/>
-      <c r="G67" s="1"/>
-      <c r="H67" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="I67" s="1">
-        <v>2</v>
-      </c>
-      <c r="J67" s="1">
-        <v>8</v>
-      </c>
-      <c r="K67" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="L67" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="M67" s="9" t="s">
-        <v>374</v>
-      </c>
-      <c r="N67" s="1"/>
-      <c r="O67" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>-osdisk</v>
-      </c>
-      <c r="P67" s="1">
-        <v>64</v>
-      </c>
-      <c r="Q67" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="R67" s="1"/>
-      <c r="S67" s="1"/>
-      <c r="T67" s="1"/>
-      <c r="U67" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v>-nic</v>
-      </c>
-      <c r="V67" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="W67" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="X67" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y67" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="Z67" s="1"/>
-      <c r="AA67" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB67" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AC67" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="AD67" s="1">
-        <v>1</v>
-      </c>
-      <c r="AE67" s="1"/>
-      <c r="AF67" s="1"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B68" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="1" t="e" cm="1">
-        <f t="array" ref="C68">UPPER(INDEX(_xlfn.TEXTSPLIT($D68, "-"), 3))</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D68" s="1"/>
-      <c r="E68" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F68" s="39"/>
-      <c r="G68" s="1"/>
-      <c r="H68" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="I68" s="1">
-        <v>2</v>
-      </c>
-      <c r="J68" s="1">
-        <v>8</v>
-      </c>
-      <c r="K68" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="L68" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="M68" s="9" t="s">
-        <v>374</v>
-      </c>
-      <c r="N68" s="1"/>
-      <c r="O68" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>-osdisk</v>
-      </c>
-      <c r="P68" s="1">
-        <v>64</v>
-      </c>
-      <c r="Q68" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="R68" s="1"/>
-      <c r="S68" s="1"/>
-      <c r="T68" s="1"/>
-      <c r="U68" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v>-nic</v>
-      </c>
-      <c r="V68" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="W68" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="X68" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y68" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="Z68" s="1"/>
-      <c r="AA68" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB68" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AC68" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="AD68" s="1">
-        <v>1</v>
-      </c>
-      <c r="AE68" s="1"/>
-      <c r="AF68" s="1"/>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B69" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="1" t="e" cm="1">
-        <f t="array" ref="C69">UPPER(INDEX(_xlfn.TEXTSPLIT($D69, "-"), 3))</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D69" s="1"/>
-      <c r="E69" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F69" s="40"/>
-      <c r="G69" s="1"/>
-      <c r="H69" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="I69" s="1">
-        <v>2</v>
-      </c>
-      <c r="J69" s="1">
-        <v>8</v>
-      </c>
-      <c r="K69" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="L69" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="M69" s="9" t="s">
-        <v>374</v>
-      </c>
-      <c r="N69" s="1"/>
-      <c r="O69" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>-osdisk</v>
-      </c>
-      <c r="P69" s="1">
-        <v>64</v>
-      </c>
-      <c r="Q69" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="R69" s="1"/>
-      <c r="S69" s="1"/>
-      <c r="T69" s="1"/>
-      <c r="U69" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v>-nic</v>
-      </c>
-      <c r="V69" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="W69" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="X69" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y69" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="Z69" s="1"/>
-      <c r="AA69" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB69" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AC69" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="AD69" s="1">
-        <v>1</v>
-      </c>
-      <c r="AE69" s="1"/>
-      <c r="AF69" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -13366,7 +12991,7 @@
         <v>23</v>
       </c>
       <c r="F54" s="16" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="G54" s="16" t="str">
         <f t="shared" si="2"/>
@@ -13415,13 +13040,13 @@
         <v>SEC</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="E55" s="17" t="s">
         <v>23</v>
       </c>
       <c r="F55" s="24" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="G55" s="17" t="str">
         <f t="shared" si="2"/>
@@ -13476,7 +13101,7 @@
         <v>23</v>
       </c>
       <c r="F56" s="16" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="G56" s="16" t="str">
         <f t="shared" si="2"/>
@@ -13531,7 +13156,7 @@
         <v>23</v>
       </c>
       <c r="F57" s="24" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="G57" s="17" t="str">
         <f t="shared" si="2"/>
@@ -13586,7 +13211,7 @@
         <v>23</v>
       </c>
       <c r="F58" s="16" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="G58" s="16" t="str">
         <f t="shared" si="2"/>
@@ -13641,7 +13266,7 @@
         <v>23</v>
       </c>
       <c r="F59" s="24" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="G59" s="17" t="str">
         <f t="shared" si="2"/>
@@ -13696,7 +13321,7 @@
         <v>23</v>
       </c>
       <c r="F60" s="16" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="G60" s="16" t="str">
         <f t="shared" si="2"/>
@@ -13745,13 +13370,13 @@
         <v>CLV</v>
       </c>
       <c r="D61" s="17" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="E61" s="17" t="s">
         <v>23</v>
       </c>
       <c r="F61" s="17" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="G61" s="17" t="str">
         <f t="shared" si="2"/>
@@ -13800,13 +13425,13 @@
         <v>CLV</v>
       </c>
       <c r="D62" s="16" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="E62" s="16" t="s">
         <v>23</v>
       </c>
       <c r="F62" s="16" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="G62" s="16" t="str">
         <f t="shared" si="2"/>
@@ -13855,13 +13480,13 @@
         <v>CLV</v>
       </c>
       <c r="D63" s="17" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="E63" s="17" t="s">
         <v>23</v>
       </c>
       <c r="F63" s="17" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="G63" s="17" t="str">
         <f t="shared" si="2"/>
@@ -13910,13 +13535,13 @@
         <v>CLV</v>
       </c>
       <c r="D64" s="16" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="E64" s="16" t="s">
         <v>23</v>
       </c>
       <c r="F64" s="16" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="G64" s="16" t="str">
         <f t="shared" si="2"/>
@@ -13965,13 +13590,13 @@
         <v>CLV</v>
       </c>
       <c r="D65" s="17" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="E65" s="17" t="s">
         <v>23</v>
       </c>
       <c r="F65" s="17" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="G65" s="17" t="str">
         <f t="shared" si="2"/>
@@ -14025,7 +13650,7 @@
         <v>23</v>
       </c>
       <c r="F66" s="16" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="G66" s="16" t="str">
         <f t="shared" si="2"/>
@@ -14035,7 +13660,7 @@
         <v>290</v>
       </c>
       <c r="I66" s="16">
-        <v>64</v>
+        <v>512</v>
       </c>
       <c r="J66" s="16" t="str">
         <f t="shared" si="3"/>
@@ -16300,7 +15925,7 @@
         <v>187</v>
       </c>
       <c r="H59" s="32" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="I59" s="32"/>
       <c r="J59" s="32"/>
@@ -16315,13 +15940,13 @@
         <v>31</v>
       </c>
       <c r="C60" s="34" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="D60" s="34" t="s">
         <v>49</v>
       </c>
       <c r="E60" s="34" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="F60" s="34" t="s">
         <v>49</v>
@@ -16330,7 +15955,7 @@
         <v>57</v>
       </c>
       <c r="H60" s="34" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="I60" s="34"/>
       <c r="J60" s="34"/>
@@ -16856,10 +16481,10 @@
     <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="11"/>
       <c r="B75" s="35" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="C75" s="35" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="D75" s="32" t="s">
         <v>49</v>
@@ -16878,17 +16503,17 @@
         <v>166</v>
       </c>
       <c r="I75" s="16" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="J75" s="16" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="K75" s="16" t="str">
         <f t="shared" si="5"/>
         <v>d-if-edmsstr01-nic</v>
       </c>
       <c r="L75" s="33" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.3">
@@ -16914,13 +16539,13 @@
         <v>56</v>
       </c>
       <c r="H76" s="34" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="I76" s="34" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="J76" s="34" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="K76" s="34" t="str">
         <f t="shared" si="5"/>
@@ -16953,13 +16578,13 @@
         <v>57</v>
       </c>
       <c r="H77" s="16" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="I77" s="16" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="J77" s="16" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="K77" s="16" t="str">
         <f t="shared" si="5"/>
@@ -16992,13 +16617,13 @@
         <v>57</v>
       </c>
       <c r="H78" s="34" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="I78" s="34" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="J78" s="34" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="K78" s="34" t="str">
         <f t="shared" si="5"/>
@@ -17031,13 +16656,13 @@
         <v>57</v>
       </c>
       <c r="H79" s="16" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="I79" s="16" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="J79" s="16" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="K79" s="16" t="str">
         <f t="shared" si="5"/>
@@ -17070,13 +16695,13 @@
         <v>57</v>
       </c>
       <c r="H80" s="34" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="I80" s="34" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="J80" s="34" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="K80" s="34" t="str">
         <f t="shared" si="5"/>
@@ -17112,7 +16737,7 @@
         <v>166</v>
       </c>
       <c r="I81" s="32" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="J81" s="16" t="s">
         <v>55</v>
